--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,6 +57,10 @@
   </si>
   <si>
     <t>班尼迪克</t>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -387,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G4"/>
+  <dimension ref="A2:G5"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -466,6 +470,29 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,13 +61,21 @@
   <si>
     <t>马</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +87,21 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2F2F2F"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -103,13 +126,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -391,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G5"/>
+  <dimension ref="A2:G7"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -493,6 +519,52 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,6 +69,14 @@
   <si>
     <t>布莱兹</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -417,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G7"/>
+  <dimension ref="A2:H7"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -427,7 +435,7 @@
     <col min="8" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,8 +457,11 @@
       <c r="G2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -472,8 +483,11 @@
       <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -495,8 +509,11 @@
       <c r="G4" s="1">
         <v>1</v>
       </c>
+      <c r="H4" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -518,8 +535,11 @@
       <c r="G5" s="1">
         <v>1</v>
       </c>
+      <c r="H5" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -541,8 +561,11 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
+      <c r="H6" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -563,6 +586,9 @@
       </c>
       <c r="G7" s="1">
         <v>1</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,6 +77,52 @@
   <si>
     <t>hide</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>likeItems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unlikeTalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unlikeEmote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unLikeItems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>likeTalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>likeEmote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defaultTalk</t>
+  </si>
+  <si>
+    <t>defaultEmote</t>
   </si>
 </sst>
 </file>
@@ -134,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -144,6 +190,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,17 +474,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H7"/>
+  <dimension ref="A2:P7"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
     <col min="3" max="4" width="15.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="7" width="15.5" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.5" style="1"/>
+    <col min="8" max="8" width="9.5" style="1"/>
+    <col min="9" max="9" width="9.5" style="4"/>
+    <col min="10" max="10" width="12.5" style="4" customWidth="1"/>
+    <col min="11" max="13" width="9.5" style="1"/>
+    <col min="14" max="14" width="11.625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,8 +514,32 @@
       <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="I2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -486,8 +564,32 @@
       <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="I3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -512,8 +614,32 @@
       <c r="H4" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1">
+        <v>30000</v>
+      </c>
+      <c r="L4" s="1">
+        <v>30001</v>
+      </c>
+      <c r="M4" s="1">
+        <v>30002</v>
+      </c>
+      <c r="N4" s="1">
+        <v>30003</v>
+      </c>
+      <c r="O4" s="1">
+        <v>30004</v>
+      </c>
+      <c r="P4" s="1">
+        <v>30005</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -538,8 +664,32 @@
       <c r="H5" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="I5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -564,8 +714,32 @@
       <c r="H6" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="1">
+        <v>30000</v>
+      </c>
+      <c r="L6" s="1">
+        <v>30001</v>
+      </c>
+      <c r="M6" s="1">
+        <v>30002</v>
+      </c>
+      <c r="N6" s="1">
+        <v>30003</v>
+      </c>
+      <c r="O6" s="1">
+        <v>30004</v>
+      </c>
+      <c r="P6" s="1">
+        <v>30005</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -589,6 +763,30 @@
       </c>
       <c r="H7" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="1">
+        <v>30000</v>
+      </c>
+      <c r="L7" s="1">
+        <v>30001</v>
+      </c>
+      <c r="M7" s="1">
+        <v>30002</v>
+      </c>
+      <c r="N7" s="1">
+        <v>30003</v>
+      </c>
+      <c r="O7" s="1">
+        <v>30004</v>
+      </c>
+      <c r="P7" s="1">
+        <v>30005</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,6 +123,14 @@
   </si>
   <si>
     <t>defaultEmote</t>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>格吉尔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -474,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:P7"/>
+  <dimension ref="A2:P9"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -539,7 +547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -786,6 +794,106 @@
         <v>30004</v>
       </c>
       <c r="P7" s="1">
+        <v>30005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="1">
+        <v>30000</v>
+      </c>
+      <c r="L8" s="1">
+        <v>30001</v>
+      </c>
+      <c r="M8" s="1">
+        <v>30002</v>
+      </c>
+      <c r="N8" s="1">
+        <v>30003</v>
+      </c>
+      <c r="O8" s="1">
+        <v>30004</v>
+      </c>
+      <c r="P8" s="1">
+        <v>30005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="1">
+        <v>30000</v>
+      </c>
+      <c r="L9" s="1">
+        <v>30001</v>
+      </c>
+      <c r="M9" s="1">
+        <v>30002</v>
+      </c>
+      <c r="N9" s="1">
+        <v>30003</v>
+      </c>
+      <c r="O9" s="1">
+        <v>30004</v>
+      </c>
+      <c r="P9" s="1">
         <v>30005</v>
       </c>
     </row>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,52 +77,6 @@
   <si>
     <t>hide</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>likeItems</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>unlikeTalk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>unlikeEmote</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>unLikeItems</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>likeTalk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>likeEmote</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defaultTalk</t>
-  </si>
-  <si>
-    <t>defaultEmote</t>
   </si>
   <si>
     <t>丝特芬妮</t>
@@ -188,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -198,9 +152,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,22 +433,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:P9"/>
+  <dimension ref="A2:H9"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
     <col min="3" max="4" width="15.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="7" width="15.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="1"/>
-    <col min="9" max="9" width="9.5" style="4"/>
-    <col min="10" max="10" width="12.5" style="4" customWidth="1"/>
-    <col min="11" max="13" width="9.5" style="1"/>
-    <col min="14" max="14" width="11.625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.5" style="1"/>
+    <col min="8" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,32 +468,8 @@
       <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -572,32 +494,8 @@
       <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -622,32 +520,8 @@
       <c r="H4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="1">
-        <v>30000</v>
-      </c>
-      <c r="L4" s="1">
-        <v>30001</v>
-      </c>
-      <c r="M4" s="1">
-        <v>30002</v>
-      </c>
-      <c r="N4" s="1">
-        <v>30003</v>
-      </c>
-      <c r="O4" s="1">
-        <v>30004</v>
-      </c>
-      <c r="P4" s="1">
-        <v>30005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -672,32 +546,8 @@
       <c r="H5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -722,32 +572,8 @@
       <c r="H6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="1">
-        <v>30000</v>
-      </c>
-      <c r="L6" s="1">
-        <v>30001</v>
-      </c>
-      <c r="M6" s="1">
-        <v>30002</v>
-      </c>
-      <c r="N6" s="1">
-        <v>30003</v>
-      </c>
-      <c r="O6" s="1">
-        <v>30004</v>
-      </c>
-      <c r="P6" s="1">
-        <v>30005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -772,37 +598,13 @@
       <c r="H7" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="1">
-        <v>30000</v>
-      </c>
-      <c r="L7" s="1">
-        <v>30001</v>
-      </c>
-      <c r="M7" s="1">
-        <v>30002</v>
-      </c>
-      <c r="N7" s="1">
-        <v>30003</v>
-      </c>
-      <c r="O7" s="1">
-        <v>30004</v>
-      </c>
-      <c r="P7" s="1">
-        <v>30005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -822,37 +624,13 @@
       <c r="H8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="1">
-        <v>30000</v>
-      </c>
-      <c r="L8" s="1">
-        <v>30001</v>
-      </c>
-      <c r="M8" s="1">
-        <v>30002</v>
-      </c>
-      <c r="N8" s="1">
-        <v>30003</v>
-      </c>
-      <c r="O8" s="1">
-        <v>30004</v>
-      </c>
-      <c r="P8" s="1">
-        <v>30005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -871,30 +649,6 @@
       </c>
       <c r="H9" s="1" t="b">
         <v>0</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="1">
-        <v>30000</v>
-      </c>
-      <c r="L9" s="1">
-        <v>30001</v>
-      </c>
-      <c r="M9" s="1">
-        <v>30002</v>
-      </c>
-      <c r="N9" s="1">
-        <v>30003</v>
-      </c>
-      <c r="O9" s="1">
-        <v>30004</v>
-      </c>
-      <c r="P9" s="1">
-        <v>30005</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -36,9 +36,6 @@
     <t>linkCharacterId</t>
   </si>
   <si>
-    <t>zeroCreate</t>
-  </si>
-  <si>
     <t>zeroFriendShipLevel</t>
   </si>
   <si>
@@ -85,6 +82,107 @@
   <si>
     <t>格吉尔</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>琼</t>
+  </si>
+  <si>
+    <t>莎拉</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>罗伊</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>希贝儿</t>
+  </si>
+  <si>
+    <t>帕特里克</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>强尼</t>
+  </si>
+  <si>
+    <t>杰克</t>
+  </si>
+  <si>
+    <t>黛娜</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zeroCreate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -122,12 +220,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -142,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -152,6 +256,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H9"/>
+  <dimension ref="A2:H41"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -448,14 +555,14 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -480,19 +587,19 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -500,7 +607,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -526,7 +633,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -552,7 +659,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
@@ -578,7 +685,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -604,7 +711,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -630,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -648,12 +755,844 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1">
+        <v>21</v>
+      </c>
+      <c r="D22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="1">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="1">
+        <v>23</v>
+      </c>
+      <c r="D24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="1">
+        <v>24</v>
+      </c>
+      <c r="D25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="1">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="1">
+        <v>26</v>
+      </c>
+      <c r="D27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="1">
+        <v>27</v>
+      </c>
+      <c r="D28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="1">
+        <v>28</v>
+      </c>
+      <c r="D29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="1">
+        <v>29</v>
+      </c>
+      <c r="D30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="1">
+        <v>30</v>
+      </c>
+      <c r="D31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="1">
+        <v>31</v>
+      </c>
+      <c r="D32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="1">
+        <v>32</v>
+      </c>
+      <c r="D33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="1">
+        <v>33</v>
+      </c>
+      <c r="D34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="1">
+        <v>34</v>
+      </c>
+      <c r="D35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="1">
+        <v>35</v>
+      </c>
+      <c r="D36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="1">
+        <v>36</v>
+      </c>
+      <c r="D37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="1">
+        <v>37</v>
+      </c>
+      <c r="D38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="1">
+        <v>38</v>
+      </c>
+      <c r="D39" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="1">
+        <v>39</v>
+      </c>
+      <c r="D40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="1">
+        <v>40</v>
+      </c>
+      <c r="D41" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12120"/>
   </bookViews>
   <sheets>
     <sheet name="NPCData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="81">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,104 +85,239 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>莎拉</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>罗伊</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>杰克</t>
+  </si>
+  <si>
+    <t>黛娜</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zeroCreate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具店可爱的前台小姐，只要看到了她的笑脸，任何人都会被感染。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饮食店的姐妹花妹妹，是一个天真快乐的小姑娘。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饮食店的姐妹花姐姐，做事情很认真，是饮食店的看板娘。</t>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>歌女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗黑萝莉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>船长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金发女</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广场地下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>俱乐部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗黑别墅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旅馆</t>
+  </si>
+  <si>
+    <t>旅馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>村公所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旅馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女骑士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>船坞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修女</t>
+  </si>
+  <si>
+    <t>冒失的魔法学徒</t>
+  </si>
+  <si>
+    <t>镇长</t>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渔民</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吟游诗人</t>
+  </si>
+  <si>
     <t>亚度尼斯</t>
-  </si>
-  <si>
-    <t>琼</t>
-  </si>
-  <si>
-    <t>莎拉</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-  </si>
-  <si>
-    <t>罗伊</t>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-  </si>
-  <si>
-    <t>天使</t>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-  </si>
-  <si>
-    <t>希拉</t>
-  </si>
-  <si>
-    <t>希尔达</t>
-  </si>
-  <si>
-    <t>布拉德利</t>
-  </si>
-  <si>
-    <t>布莱兹</t>
-  </si>
-  <si>
-    <t>布蓝达</t>
-  </si>
-  <si>
-    <t>希贝儿</t>
-  </si>
-  <si>
-    <t>帕特里克</t>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-  </si>
-  <si>
-    <t>梅林</t>
-  </si>
-  <si>
-    <t>摩尔根</t>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-  </si>
-  <si>
-    <t>考波特</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-  </si>
-  <si>
-    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>强尼</t>
-  </si>
-  <si>
-    <t>杰克</t>
-  </si>
-  <si>
-    <t>黛娜</t>
-  </si>
-  <si>
-    <t>阿普敦</t>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-  </si>
-  <si>
-    <t>莱特</t>
-  </si>
-  <si>
-    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>女仆</t>
   </si>
   <si>
     <t>阿尔杰农</t>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zeroCreate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -246,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -258,6 +394,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -540,17 +679,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H41"/>
+  <dimension ref="A2:K41"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
     <col min="3" max="4" width="15.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" customWidth="1"/>
-    <col min="6" max="7" width="15.5" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.5" style="1"/>
+    <col min="5" max="5" width="17" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="15.5" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="1"/>
+    <col min="9" max="9" width="40.25" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,8 +716,11 @@
       <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -587,7 +731,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -601,8 +745,11 @@
       <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -628,7 +775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -654,7 +801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -680,7 +827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -706,7 +853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -732,7 +879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -758,12 +905,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -783,13 +930,16 @@
       <c r="H10" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+      <c r="I10" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
+      <c r="B11" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -809,19 +959,22 @@
       <c r="H11" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>19</v>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -833,15 +986,15 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>20</v>
+      <c r="B13" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C13" s="1">
         <v>12</v>
@@ -861,13 +1014,19 @@
       <c r="H13" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" s="1">
         <v>13</v>
@@ -888,12 +1047,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+    <row r="15" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>22</v>
+      <c r="B15" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C15" s="1">
         <v>14</v>
@@ -913,13 +1072,16 @@
       <c r="H15" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1">
         <v>15</v>
@@ -940,12 +1102,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+    <row r="17" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>24</v>
+      <c r="B17" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="C17" s="1">
         <v>16</v>
@@ -965,13 +1127,16 @@
       <c r="H17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+      <c r="I17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>25</v>
+      <c r="B18" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="C18" s="1">
         <v>17</v>
@@ -991,13 +1156,16 @@
       <c r="H18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>26</v>
+      <c r="B19" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C19" s="1">
         <v>18</v>
@@ -1017,13 +1185,19 @@
       <c r="H19" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
+      <c r="I19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>27</v>
+      <c r="B20" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C20" s="1">
         <v>19</v>
@@ -1044,12 +1218,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>28</v>
+      <c r="B21" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C21" s="1">
         <v>20</v>
@@ -1070,14 +1244,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="1">
+      <c r="B22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="5">
         <v>21</v>
       </c>
       <c r="D22" s="1" t="b">
@@ -1095,13 +1269,19 @@
       <c r="H22" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>30</v>
+      <c r="B23" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C23" s="1">
         <v>22</v>
@@ -1121,13 +1301,19 @@
       <c r="H23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
+      <c r="I23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>31</v>
+      <c r="B24" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C24" s="1">
         <v>23</v>
@@ -1147,13 +1333,19 @@
       <c r="H24" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
+      <c r="I24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>32</v>
+      <c r="B25" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C25" s="1">
         <v>24</v>
@@ -1173,13 +1365,19 @@
       <c r="H25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>33</v>
+      <c r="B26" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C26" s="1">
         <v>25</v>
@@ -1199,13 +1397,16 @@
       <c r="H26" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
+      <c r="I26" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>34</v>
+      <c r="B27" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C27" s="1">
         <v>26</v>
@@ -1225,13 +1426,16 @@
       <c r="H27" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
+      <c r="I27" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>35</v>
+      <c r="B28" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="C28" s="1">
         <v>27</v>
@@ -1251,13 +1455,19 @@
       <c r="H28" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
+      <c r="I28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>36</v>
+      <c r="B29" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1277,13 +1487,19 @@
       <c r="H29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
+      <c r="I29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>37</v>
+      <c r="B30" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C30" s="1">
         <v>29</v>
@@ -1303,13 +1519,19 @@
       <c r="H30" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
+      <c r="I30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>38</v>
+      <c r="B31" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C31" s="1">
         <v>30</v>
@@ -1329,13 +1551,19 @@
       <c r="H31" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
+      <c r="I31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>39</v>
+      <c r="B32" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="C32" s="1">
         <v>31</v>
@@ -1355,13 +1583,16 @@
       <c r="H32" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C33" s="1">
         <v>32</v>
@@ -1382,12 +1613,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C34" s="1">
         <v>33</v>
@@ -1408,12 +1639,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>48</v>
+      <c r="B35" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C35" s="1">
         <v>34</v>
@@ -1434,11 +1665,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="1">
@@ -1459,13 +1690,19 @@
       <c r="H36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>43</v>
+      <c r="B37" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="C37" s="1">
         <v>36</v>
@@ -1486,12 +1723,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>44</v>
+      <c r="B38" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C38" s="1">
         <v>37</v>
@@ -1512,12 +1749,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>45</v>
+      <c r="B39" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="C39" s="1">
         <v>38</v>
@@ -1537,13 +1774,19 @@
       <c r="H39" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>46</v>
+      <c r="B40" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="C40" s="1">
         <v>39</v>
@@ -1564,12 +1807,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
+    <row r="41" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>47</v>
+      <c r="B41" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C41" s="1">
         <v>40</v>
@@ -1588,6 +1831,9 @@
       </c>
       <c r="H41" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1595,4 +1841,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="H13:I15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="13" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H13">
+        <f>2147483647/100000</f>
+        <v>21474.836469999998</v>
+      </c>
+    </row>
+    <row r="15" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <v>21475</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,41 +216,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>广场地下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>俱乐部</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暗黑别墅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>旅馆</t>
-  </si>
-  <si>
-    <t>旅馆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>村公所</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>旅馆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>女骑士</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>船坞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>希拉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -318,6 +287,10 @@
   </si>
   <si>
     <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -679,19 +652,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K41"/>
+  <dimension ref="A2:I42"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
     <col min="3" max="4" width="15.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="15.5" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" customWidth="1"/>
+    <col min="6" max="7" width="15.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.5" style="1"/>
     <col min="9" max="9" width="40.25" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -720,7 +693,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -749,7 +722,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -775,7 +748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -801,7 +774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -827,7 +800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -853,7 +826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -879,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -905,12 +878,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -931,15 +904,15 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -960,10 +933,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -989,7 +962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1017,11 +990,8 @@
       <c r="I13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1047,7 +1017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1076,7 +1046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1102,7 +1072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1131,12 +1101,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1">
         <v>17</v>
@@ -1157,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1186,13 +1156,10 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1218,7 +1185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1244,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1272,16 +1239,13 @@
       <c r="I22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1">
         <v>22</v>
@@ -1302,13 +1266,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -1334,13 +1295,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1368,16 +1326,13 @@
       <c r="I25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C26" s="1">
         <v>25</v>
@@ -1398,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -1427,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -1458,11 +1413,8 @@
       <c r="I28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -1490,11 +1442,8 @@
       <c r="I29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -1522,11 +1471,8 @@
       <c r="I30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -1554,16 +1500,13 @@
       <c r="I31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C32" s="1">
         <v>31</v>
@@ -1584,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -1613,7 +1556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -1639,7 +1582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1665,7 +1608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -1691,18 +1634,15 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C37" s="1">
         <v>36</v>
@@ -1723,12 +1663,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C38" s="1">
         <v>37</v>
@@ -1749,12 +1689,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C39" s="1">
         <v>38</v>
@@ -1777,16 +1717,13 @@
       <c r="I39" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C40" s="1">
         <v>39</v>
@@ -1807,7 +1744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -1834,6 +1771,32 @@
       </c>
       <c r="I41" s="1" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="1">
+        <v>213</v>
+      </c>
+      <c r="D42" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+      <c r="H42" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="85">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -292,6 +292,46 @@
   <si>
     <t>纺织婆婆</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>functionIds</t>
+  </si>
+  <si>
+    <t>shopName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>植物店</t>
+  </si>
+  <si>
+    <t>家具店</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物店</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerOperateEventId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>nextTalkEventId</t>
   </si>
 </sst>
 </file>
@@ -652,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I42"/>
+  <dimension ref="A2:M42"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -661,10 +701,11 @@
     <col min="6" max="7" width="15.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.5" style="1"/>
     <col min="9" max="9" width="40.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.5" style="1"/>
+    <col min="10" max="11" width="9.5" style="2"/>
+    <col min="12" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -692,8 +733,20 @@
       <c r="I2" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -721,8 +774,20 @@
       <c r="I3" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -747,8 +812,17 @@
       <c r="H4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -773,8 +847,14 @@
       <c r="H5" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -799,8 +879,20 @@
       <c r="H6" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="2">
+        <v>8003</v>
+      </c>
+      <c r="M6" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -825,8 +917,20 @@
       <c r="H7" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="2">
+        <v>8002</v>
+      </c>
+      <c r="M7" s="2">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -851,8 +955,20 @@
       <c r="H8" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="2">
+        <v>8004</v>
+      </c>
+      <c r="M8" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -877,8 +993,20 @@
       <c r="H9" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="2">
+        <v>8005</v>
+      </c>
+      <c r="M9" s="2">
+        <v>8005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -906,8 +1034,17 @@
       <c r="I10" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -935,8 +1072,17 @@
       <c r="I11" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -961,8 +1107,17 @@
       <c r="H12" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -990,8 +1145,17 @@
       <c r="I13" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1016,8 +1180,17 @@
       <c r="H14" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1045,8 +1218,20 @@
       <c r="I15" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1071,8 +1256,17 @@
       <c r="H16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1100,8 +1294,17 @@
       <c r="I17" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1129,8 +1332,17 @@
       <c r="I18" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1158,8 +1370,17 @@
       <c r="I19" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1184,8 +1405,17 @@
       <c r="H20" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1210,8 +1440,17 @@
       <c r="H21" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1239,8 +1478,17 @@
       <c r="I22" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1268,8 +1516,17 @@
       <c r="I23" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -1297,8 +1554,17 @@
       <c r="I24" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1326,8 +1592,17 @@
       <c r="I25" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1355,8 +1630,17 @@
       <c r="I26" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -1384,8 +1668,17 @@
       <c r="I27" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -1413,8 +1706,17 @@
       <c r="I28" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -1442,8 +1744,17 @@
       <c r="I29" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -1471,8 +1782,17 @@
       <c r="I30" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -1500,8 +1820,17 @@
       <c r="I31" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -1529,8 +1858,17 @@
       <c r="I32" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -1555,8 +1893,17 @@
       <c r="H33" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -1581,8 +1928,17 @@
       <c r="H34" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1607,8 +1963,17 @@
       <c r="H35" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -1636,8 +2001,17 @@
       <c r="I36" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J36" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1662,8 +2036,14 @@
       <c r="H37" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -1688,8 +2068,14 @@
       <c r="H38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -1717,8 +2103,14 @@
       <c r="I39" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1743,8 +2135,14 @@
       <c r="H40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -1772,8 +2170,14 @@
       <c r="I41" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1796,6 +2200,12 @@
         <v>1</v>
       </c>
       <c r="H42" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -10,6 +10,9 @@
     <sheet name="NPCData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$M$2:$N$2</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -20,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="159">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,261 +80,495 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>莎拉</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>罗伊</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>杰克</t>
+  </si>
+  <si>
+    <t>黛娜</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zeroCreate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具店可爱的前台小姐，只要看到了她的笑脸，任何人都会被感染。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饮食店的姐妹花妹妹，是一个天真快乐的小姑娘。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饮食店的姐妹花姐姐，做事情很认真，是饮食店的看板娘。</t>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>functionIds</t>
+  </si>
+  <si>
+    <t>shopName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>植物店</t>
+  </si>
+  <si>
+    <t>家具店</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物店</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerOperateEventId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>nextTalkEventId</t>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+  </si>
+  <si>
     <t>丝特芬妮</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>格吉尔</t>
+  </si>
+  <si>
+    <t>格吉尔</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>莎拉</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-  </si>
-  <si>
-    <t>罗伊</t>
-  </si>
-  <si>
-    <t>天使</t>
-  </si>
-  <si>
-    <t>希尔达</t>
-  </si>
-  <si>
-    <t>考波特</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-  </si>
-  <si>
-    <t>杰克</t>
-  </si>
-  <si>
-    <t>黛娜</t>
-  </si>
-  <si>
-    <t>黛芙妮</t>
+    <t>小镇上的富商，经营家具生意，年轻时曾游走大陆，交友很广泛。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具屋的老奶奶，无论对待谁都很和蔼，除了帕特里克爷爷，不知道他们年轻时发生了什么呢？</t>
+  </si>
+  <si>
+    <t>热心肠的男孩，干什么事都很热血，住在道具屋，很在意玛德琳奶奶。</t>
+  </si>
+  <si>
+    <t>和姐姐一起生活在动物店，每日都重复着平静的生活，一直幻想着成为传说中的英雄。</t>
+  </si>
+  <si>
+    <t>小镇的镇长，对年轻一辈很照顾，常常一个人在广场上回忆逝去的时光。</t>
+  </si>
+  <si>
+    <t>小镇的防卫官，从王国精锐部队退役的将军，用心的维护着小镇的安全</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作为单亲妈妈抚养了一对双胞胎成长，厨艺十分精湛，她的料理很受人们欢迎。</t>
+  </si>
+  <si>
+    <t>工具店的老板，因为大哥一家在一场意外中逝去，立下誓言要守护自己的侄子，经常会对侄子的行为而感到无奈。</t>
+  </si>
+  <si>
+    <t>跟着叔叔在工具店工作，但对这份工作很没有兴趣，整日里打不起精神，实际上是一个很聪明的男孩。</t>
+  </si>
+  <si>
+    <t>热衷于考古的学者，在小镇附近发现了古代帝国遗址的线索，所以留在小镇中。</t>
+  </si>
+  <si>
+    <t>小镇中的吟游诗人，对自然的关注远远大于人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘的女魔法师，虽然看起来很年轻，实际却是在小镇形成之前就已经在此生活了。</t>
+  </si>
+  <si>
+    <t>在很多年前因为未知的原因迁入小镇，独自抚养弟弟长大，是一个安静的美人。</t>
+  </si>
+  <si>
+    <t>来自异国度的流浪舞女，在小镇休整，和俱乐部老板的关系密切。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒失的魔法学徒，在婴儿时期被梅林捡到，对师父很崇拜，时常对自己的笨拙的魔法天赋感到苦恼。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年轻的士兵，责任感很强，每天都会非常勤奋的巡视小镇。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教堂的修女，要负责整个教堂的运转，既温柔又能干</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>住在广场地下的神秘婆婆，她的占卜很灵，可以预知一些未来的事情。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具店雇佣的女仆，是一个认真负责的好姑娘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在王国骑士学院学习，立志成为骑士，家庭发生变故后回到小镇和妹妹一起经营客栈。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个家族没落的贵族子弟，与管家相依为命。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体格健壮的渔夫，经营着一家鱼店。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验丰富的船长，拥有丰富的见闻。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年轻的实习水手，跟随船长努力的学习航海知识。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在小镇休整的游侠，传说在很多事件中都曾出现过他的身影。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从小在教堂长大，对牧师这个职业似乎不是很喜欢。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和姐姐经营着一家客栈，虽然年纪小，却是做生意的一把好手。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>独居的纺织婆婆，一直致力于使用纺织给大家带来美丽。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾德文娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>talkForFriendShip</t>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+  </si>
+  <si>
+    <t>地点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>玛德琳</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>琼</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>希贝儿</t>
+  </si>
+  <si>
+    <t>帕特里克</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>强尼</t>
   </si>
   <si>
     <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zeroCreate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>text</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>家具店可爱的前台小姐，只要看到了她的笑脸，任何人都会被感染。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>饮食店的姐妹花妹妹，是一个天真快乐的小姑娘。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>饮食店的姐妹花姐姐，做事情很认真，是饮食店的看板娘。</t>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>摩尔根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>歌女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暗黑萝莉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>船长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游侠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>学者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金发女</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>女骑士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希贝儿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>艾琳娜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>琼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修女</t>
-  </si>
-  <si>
-    <t>冒失的魔法学徒</t>
-  </si>
-  <si>
-    <t>镇长</t>
-  </si>
-  <si>
-    <t>梅林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔法师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>渔民</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>管家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吟游诗人</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牧师</t>
-  </si>
-  <si>
-    <t>女仆</t>
   </si>
   <si>
     <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>functionIds</t>
-  </si>
-  <si>
-    <t>shopName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>植物店</t>
-  </si>
-  <si>
-    <t>家具店</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>动物店</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>playerOperateEventId</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>nextTalkEventId</t>
+  </si>
+  <si>
+    <t>0,70032</t>
+  </si>
+  <si>
+    <t>0,70002</t>
+  </si>
+  <si>
+    <t>0,70001</t>
+  </si>
+  <si>
+    <t>0,70003</t>
+  </si>
+  <si>
+    <t>0,70004</t>
+  </si>
+  <si>
+    <t>0,70005</t>
+  </si>
+  <si>
+    <t>0,70006</t>
+  </si>
+  <si>
+    <t>0,70007</t>
+  </si>
+  <si>
+    <t>0,70008</t>
+  </si>
+  <si>
+    <t>0,70009</t>
+  </si>
+  <si>
+    <t>0,70010</t>
+  </si>
+  <si>
+    <t>0,70011</t>
+  </si>
+  <si>
+    <t>0,70012</t>
+  </si>
+  <si>
+    <t>0,70013</t>
+  </si>
+  <si>
+    <t>0,70014</t>
+  </si>
+  <si>
+    <t>0,70015</t>
+  </si>
+  <si>
+    <t>0,70016</t>
+  </si>
+  <si>
+    <t>0,70017</t>
+  </si>
+  <si>
+    <t>0,70018</t>
+  </si>
+  <si>
+    <t>0,70019</t>
+  </si>
+  <si>
+    <t>0,70020</t>
+  </si>
+  <si>
+    <t>0,70021</t>
+  </si>
+  <si>
+    <t>0,70022</t>
+  </si>
+  <si>
+    <t>0,70023</t>
+  </si>
+  <si>
+    <t>0,70024</t>
+  </si>
+  <si>
+    <t>0,70025</t>
+  </si>
+  <si>
+    <t>0,70026</t>
+  </si>
+  <si>
+    <t>0,70027</t>
+  </si>
+  <si>
+    <t>0,70028</t>
+  </si>
+  <si>
+    <t>0,70029</t>
+  </si>
+  <si>
+    <t>0,70030</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>0,70031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -692,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:M42"/>
+  <dimension ref="A2:N42"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -705,7 +942,7 @@
     <col min="12" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -731,22 +968,25 @@
         <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="42.75" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -757,7 +997,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -772,27 +1012,30 @@
         <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -812,17 +1055,23 @@
       <c r="H4" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="J4" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="L4" s="2">
         <v>8001</v>
       </c>
       <c r="M4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+        <v>8001</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -853,8 +1102,11 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -879,20 +1131,26 @@
       <c r="H6" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I6" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J6" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="L6" s="2">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="M6" s="2">
-        <v>8003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+        <v>8001</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -917,25 +1175,31 @@
       <c r="H7" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I7" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J7" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="L7" s="2">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="M7" s="2">
-        <v>8002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+        <v>8001</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -955,25 +1219,31 @@
       <c r="H8" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I8" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J8" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="L8" s="2">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="M8" s="2">
-        <v>8004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+        <v>8001</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -993,25 +1263,31 @@
       <c r="H9" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I9" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J9" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="L9" s="2">
-        <v>8005</v>
+        <v>8001</v>
       </c>
       <c r="M9" s="2">
-        <v>8005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+        <v>8001</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -1032,24 +1308,27 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L10" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M10" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -1070,24 +1349,27 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L11" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M11" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1">
         <v>11</v>
@@ -1108,21 +1390,24 @@
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L12" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M12" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1">
         <v>12</v>
@@ -1143,24 +1428,27 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L13" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M13" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1">
         <v>13</v>
@@ -1181,21 +1469,24 @@
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L14" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M14" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1">
         <v>14</v>
@@ -1216,27 +1507,30 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="L15" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M15" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1">
         <v>15</v>
@@ -1257,21 +1551,24 @@
         <v>1</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L16" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M16" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17" s="1">
         <v>16</v>
@@ -1292,24 +1589,27 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L17" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M17" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1">
         <v>17</v>
@@ -1330,24 +1630,27 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L18" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M18" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
         <v>18</v>
@@ -1368,24 +1671,27 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L19" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M19" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1">
         <v>19</v>
@@ -1405,22 +1711,28 @@
       <c r="H20" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I20" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="J20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L20" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M20" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C21" s="1">
         <v>20</v>
@@ -1440,22 +1752,28 @@
       <c r="H21" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I21" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L21" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M21" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C22" s="5">
         <v>21</v>
@@ -1476,24 +1794,27 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L22" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M22" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C23" s="1">
         <v>22</v>
@@ -1514,24 +1835,27 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L23" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M23" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C24" s="1">
         <v>23</v>
@@ -1552,24 +1876,27 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L24" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M24" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" s="1">
         <v>24</v>
@@ -1590,24 +1917,27 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L25" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M25" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1">
         <v>25</v>
@@ -1628,24 +1958,27 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L26" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M26" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="1">
         <v>26</v>
@@ -1666,24 +1999,27 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L27" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M27" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C28" s="1">
         <v>27</v>
@@ -1704,24 +2040,27 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L28" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M28" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1742,24 +2081,27 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L29" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M29" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C30" s="1">
         <v>29</v>
@@ -1780,24 +2122,27 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L30" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M30" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C31" s="1">
         <v>30</v>
@@ -1818,24 +2163,27 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L31" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M31" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C32" s="1">
         <v>31</v>
@@ -1856,24 +2204,27 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L32" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M32" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C33" s="1">
         <v>32</v>
@@ -1894,21 +2245,24 @@
         <v>1</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L33" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M33" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C34" s="1">
         <v>33</v>
@@ -1929,21 +2283,24 @@
         <v>1</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L34" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M34" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C35" s="1">
         <v>34</v>
@@ -1963,22 +2320,28 @@
       <c r="H35" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="I35" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="J35" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L35" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M35" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C36" s="1">
         <v>35</v>
@@ -1999,24 +2362,27 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="L36" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M36" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C37" s="1">
         <v>36</v>
@@ -2036,19 +2402,25 @@
       <c r="H37" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L37" s="1">
-        <v>0</v>
-      </c>
-      <c r="M37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L37" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M37" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C38" s="1">
         <v>37</v>
@@ -2068,19 +2440,25 @@
       <c r="H38" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L38" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M38" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C39" s="1">
         <v>38</v>
@@ -2101,21 +2479,24 @@
         <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="L39" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M39" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C40" s="1">
         <v>39</v>
@@ -2135,19 +2516,25 @@
       <c r="H40" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L40" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M40" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C41" s="1">
         <v>40</v>
@@ -2168,21 +2555,24 @@
         <v>0</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="L41" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M41" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1">
         <v>213</v>
@@ -2202,11 +2592,17 @@
       <c r="H42" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1">
-        <v>0</v>
+      <c r="I42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L42" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M42" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2218,21 +2614,282 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="H13:I15"/>
+  <dimension ref="H2:N34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="13" max="13" width="16.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="13" spans="8:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N3">
+        <v>70001</v>
+      </c>
+    </row>
+    <row r="4" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N4">
+        <v>70002</v>
+      </c>
+    </row>
+    <row r="5" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5">
+        <v>70003</v>
+      </c>
+    </row>
+    <row r="6" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M6" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6">
+        <v>70004</v>
+      </c>
+    </row>
+    <row r="7" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M7" t="s">
+        <v>105</v>
+      </c>
+      <c r="N7">
+        <v>70005</v>
+      </c>
+    </row>
+    <row r="8" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M8" t="s">
+        <v>106</v>
+      </c>
+      <c r="N8">
+        <v>70006</v>
+      </c>
+    </row>
+    <row r="9" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9">
+        <v>70007</v>
+      </c>
+    </row>
+    <row r="10" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M10" t="s">
+        <v>107</v>
+      </c>
+      <c r="N10">
+        <v>70008</v>
+      </c>
+    </row>
+    <row r="11" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M11" t="s">
+        <v>108</v>
+      </c>
+      <c r="N11">
+        <v>70009</v>
+      </c>
+    </row>
+    <row r="12" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M12" t="s">
+        <v>109</v>
+      </c>
+      <c r="N12">
+        <v>70010</v>
+      </c>
+    </row>
+    <row r="13" spans="8:14" x14ac:dyDescent="0.2">
       <c r="H13">
         <f>2147483647/100000</f>
         <v>21474.836469999998</v>
       </c>
-    </row>
-    <row r="15" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="M13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13">
+        <v>70011</v>
+      </c>
+    </row>
+    <row r="14" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M14" t="s">
+        <v>110</v>
+      </c>
+      <c r="N14">
+        <v>70012</v>
+      </c>
+    </row>
+    <row r="15" spans="8:14" x14ac:dyDescent="0.2">
       <c r="I15">
         <v>21475</v>
       </c>
+      <c r="M15" t="s">
+        <v>111</v>
+      </c>
+      <c r="N15">
+        <v>70013</v>
+      </c>
+    </row>
+    <row r="16" spans="8:14" x14ac:dyDescent="0.2">
+      <c r="M16" t="s">
+        <v>112</v>
+      </c>
+      <c r="N16">
+        <v>70014</v>
+      </c>
+    </row>
+    <row r="17" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M17" t="s">
+        <v>113</v>
+      </c>
+      <c r="N17">
+        <v>70015</v>
+      </c>
+    </row>
+    <row r="18" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M18" t="s">
+        <v>114</v>
+      </c>
+      <c r="N18">
+        <v>70016</v>
+      </c>
+    </row>
+    <row r="19" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M19" t="s">
+        <v>115</v>
+      </c>
+      <c r="N19">
+        <v>70017</v>
+      </c>
+    </row>
+    <row r="20" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M20" t="s">
+        <v>116</v>
+      </c>
+      <c r="N20">
+        <v>70018</v>
+      </c>
+    </row>
+    <row r="21" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M21" t="s">
+        <v>117</v>
+      </c>
+      <c r="N21">
+        <v>70019</v>
+      </c>
+    </row>
+    <row r="22" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M22" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22">
+        <v>70020</v>
+      </c>
+    </row>
+    <row r="23" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23">
+        <v>70021</v>
+      </c>
+    </row>
+    <row r="24" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24">
+        <v>70022</v>
+      </c>
+    </row>
+    <row r="25" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M25" t="s">
+        <v>118</v>
+      </c>
+      <c r="N25">
+        <v>70023</v>
+      </c>
+    </row>
+    <row r="26" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M26" t="s">
+        <v>119</v>
+      </c>
+      <c r="N26">
+        <v>70024</v>
+      </c>
+    </row>
+    <row r="27" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M27" t="s">
+        <v>120</v>
+      </c>
+      <c r="N27">
+        <v>70025</v>
+      </c>
+    </row>
+    <row r="28" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M28" t="s">
+        <v>121</v>
+      </c>
+      <c r="N28">
+        <v>70026</v>
+      </c>
+    </row>
+    <row r="29" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M29" t="s">
+        <v>122</v>
+      </c>
+      <c r="N29">
+        <v>70027</v>
+      </c>
+    </row>
+    <row r="30" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M30" t="s">
+        <v>123</v>
+      </c>
+      <c r="N30">
+        <v>70028</v>
+      </c>
+    </row>
+    <row r="31" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M31" t="s">
+        <v>124</v>
+      </c>
+      <c r="N31">
+        <v>70029</v>
+      </c>
+    </row>
+    <row r="32" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M32" t="s">
+        <v>25</v>
+      </c>
+      <c r="N32">
+        <v>70030</v>
+      </c>
+    </row>
+    <row r="33" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M33" t="s">
+        <v>125</v>
+      </c>
+      <c r="N33">
+        <v>70031</v>
+      </c>
+    </row>
+    <row r="34" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M34" t="s">
+        <v>9</v>
+      </c>
+      <c r="N34">
+        <v>70032</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="M2:N2"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -1486,7 +1486,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1">
         <v>14</v>
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>58</v>
@@ -1568,7 +1568,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1">
         <v>16</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>58</v>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="165">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -384,190 +384,212 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>talkForFriendShip</t>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+  </si>
+  <si>
+    <t>地点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>玛德琳</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>琼</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>希贝儿</t>
+  </si>
+  <si>
+    <t>帕特里克</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>强尼</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+  </si>
+  <si>
+    <t>0,70032</t>
+  </si>
+  <si>
+    <t>0,70002</t>
+  </si>
+  <si>
+    <t>0,70001</t>
+  </si>
+  <si>
+    <t>0,70003</t>
+  </si>
+  <si>
+    <t>0,70004</t>
+  </si>
+  <si>
+    <t>0,70005</t>
+  </si>
+  <si>
+    <t>0,70006</t>
+  </si>
+  <si>
+    <t>0,70007</t>
+  </si>
+  <si>
+    <t>0,70008</t>
+  </si>
+  <si>
+    <t>0,70009</t>
+  </si>
+  <si>
+    <t>0,70010</t>
+  </si>
+  <si>
+    <t>0,70011</t>
+  </si>
+  <si>
+    <t>0,70012</t>
+  </si>
+  <si>
+    <t>0,70013</t>
+  </si>
+  <si>
+    <t>0,70014</t>
+  </si>
+  <si>
+    <t>0,70015</t>
+  </si>
+  <si>
+    <t>0,70016</t>
+  </si>
+  <si>
+    <t>0,70017</t>
+  </si>
+  <si>
+    <t>0,70018</t>
+  </si>
+  <si>
+    <t>0,70019</t>
+  </si>
+  <si>
+    <t>0,70020</t>
+  </si>
+  <si>
+    <t>0,70021</t>
+  </si>
+  <si>
+    <t>0,70022</t>
+  </si>
+  <si>
+    <t>0,70023</t>
+  </si>
+  <si>
+    <t>0,70024</t>
+  </si>
+  <si>
+    <t>0,70025</t>
+  </si>
+  <si>
+    <t>0,70026</t>
+  </si>
+  <si>
+    <t>0,70027</t>
+  </si>
+  <si>
+    <t>0,70028</t>
+  </si>
+  <si>
+    <t>0,70029</t>
+  </si>
+  <si>
+    <t>0,70030</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>0,70031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>艾德文娜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>talkForFriendShip</t>
-  </si>
-  <si>
-    <t>List&lt;int2&gt;</t>
-  </si>
-  <si>
-    <t>地点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-  </si>
-  <si>
-    <t>玛德琳</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-  </si>
-  <si>
-    <t>琼</t>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-  </si>
-  <si>
-    <t>希拉</t>
-  </si>
-  <si>
-    <t>布拉德利</t>
-  </si>
-  <si>
-    <t>布蓝达</t>
-  </si>
-  <si>
-    <t>希贝儿</t>
-  </si>
-  <si>
-    <t>帕特里克</t>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-  </si>
-  <si>
-    <t>梅林</t>
-  </si>
-  <si>
-    <t>摩尔根</t>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-  </si>
-  <si>
-    <t>强尼</t>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-  </si>
-  <si>
-    <t>阿普敦</t>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-  </si>
-  <si>
-    <t>莱特</t>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-  </si>
-  <si>
-    <t>0,70032</t>
-  </si>
-  <si>
-    <t>0,70002</t>
-  </si>
-  <si>
-    <t>0,70001</t>
-  </si>
-  <si>
-    <t>0,70003</t>
-  </si>
-  <si>
-    <t>0,70004</t>
-  </si>
-  <si>
-    <t>0,70005</t>
-  </si>
-  <si>
-    <t>0,70006</t>
-  </si>
-  <si>
-    <t>0,70007</t>
-  </si>
-  <si>
-    <t>0,70008</t>
-  </si>
-  <si>
-    <t>0,70009</t>
-  </si>
-  <si>
-    <t>0,70010</t>
-  </si>
-  <si>
-    <t>0,70011</t>
-  </si>
-  <si>
-    <t>0,70012</t>
-  </si>
-  <si>
-    <t>0,70013</t>
-  </si>
-  <si>
-    <t>0,70014</t>
-  </si>
-  <si>
-    <t>0,70015</t>
-  </si>
-  <si>
-    <t>0,70016</t>
-  </si>
-  <si>
-    <t>0,70017</t>
-  </si>
-  <si>
-    <t>0,70018</t>
-  </si>
-  <si>
-    <t>0,70019</t>
-  </si>
-  <si>
-    <t>0,70020</t>
-  </si>
-  <si>
-    <t>0,70021</t>
-  </si>
-  <si>
-    <t>0,70022</t>
-  </si>
-  <si>
-    <t>0,70023</t>
-  </si>
-  <si>
-    <t>0,70024</t>
-  </si>
-  <si>
-    <t>0,70025</t>
-  </si>
-  <si>
-    <t>0,70026</t>
-  </si>
-  <si>
-    <t>0,70027</t>
-  </si>
-  <si>
-    <t>0,70028</t>
-  </si>
-  <si>
-    <t>0,70029</t>
-  </si>
-  <si>
-    <t>0,70030</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>0,70031</t>
+    <t>饮食店</t>
+  </si>
+  <si>
+    <t>装备店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法商店</t>
+  </si>
+  <si>
+    <t>鱼店</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -983,7 +1005,7 @@
         <v>63</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1027,7 +1049,7 @@
         <v>65</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1035,7 +1057,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1068,7 +1090,7 @@
         <v>8001</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -1103,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1147,7 +1169,7 @@
         <v>8001</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1191,7 +1213,7 @@
         <v>8001</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1235,7 +1257,7 @@
         <v>8001</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1279,7 +1301,7 @@
         <v>8001</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1320,7 +1342,7 @@
         <v>8001</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1361,7 +1383,7 @@
         <v>8001</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1399,7 +1421,7 @@
         <v>8001</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1440,7 +1462,7 @@
         <v>8001</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1478,7 +1500,7 @@
         <v>8001</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1522,7 +1544,7 @@
         <v>8001</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1560,7 +1582,7 @@
         <v>8001</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1594,6 +1616,9 @@
       <c r="J17" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="K17" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="L17" s="2">
         <v>8001</v>
       </c>
@@ -1601,7 +1626,7 @@
         <v>8001</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1642,7 +1667,7 @@
         <v>8001</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1683,7 +1708,7 @@
         <v>8001</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1717,6 +1742,9 @@
       <c r="J20" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="K20" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="L20" s="2">
         <v>8001</v>
       </c>
@@ -1724,7 +1752,7 @@
         <v>8001</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1765,7 +1793,7 @@
         <v>8001</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1806,7 +1834,7 @@
         <v>8001</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1840,6 +1868,9 @@
       <c r="J23" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="K23" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="L23" s="2">
         <v>8001</v>
       </c>
@@ -1847,7 +1878,7 @@
         <v>8001</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1888,7 +1919,7 @@
         <v>8001</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -1929,7 +1960,7 @@
         <v>8001</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1963,6 +1994,9 @@
       <c r="J26" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="K26" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="L26" s="2">
         <v>8001</v>
       </c>
@@ -1970,7 +2004,7 @@
         <v>8001</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -2004,6 +2038,9 @@
       <c r="J27" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="K27" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="L27" s="2">
         <v>8001</v>
       </c>
@@ -2011,7 +2048,7 @@
         <v>8001</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -2052,7 +2089,7 @@
         <v>8001</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2093,7 +2130,7 @@
         <v>8001</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2134,7 +2171,7 @@
         <v>8001</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2175,7 +2212,7 @@
         <v>8001</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2216,7 +2253,7 @@
         <v>8001</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -2254,7 +2291,7 @@
         <v>8001</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -2292,7 +2329,7 @@
         <v>8001</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2333,7 +2370,7 @@
         <v>8001</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -2374,7 +2411,7 @@
         <v>8001</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2405,6 +2442,9 @@
       <c r="I37" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="K37" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="L37" s="2">
         <v>8001</v>
       </c>
@@ -2412,7 +2452,7 @@
         <v>8001</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -2443,6 +2483,9 @@
       <c r="I38" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="K38" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="L38" s="2">
         <v>8001</v>
       </c>
@@ -2450,7 +2493,7 @@
         <v>8001</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2488,7 +2531,7 @@
         <v>8001</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2526,7 +2569,7 @@
         <v>8001</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2557,6 +2600,9 @@
       <c r="I41" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="K41" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="L41" s="2">
         <v>8001</v>
       </c>
@@ -2564,7 +2610,7 @@
         <v>8001</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2572,7 +2618,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="C42" s="1">
         <v>213</v>
@@ -2595,6 +2641,9 @@
       <c r="I42" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="K42" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="L42" s="2">
         <v>8001</v>
       </c>
@@ -2602,7 +2651,7 @@
         <v>8001</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2622,12 +2671,12 @@
   <sheetData>
     <row r="2" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N3">
         <v>70001</v>
@@ -2635,7 +2684,7 @@
     </row>
     <row r="4" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N4">
         <v>70002</v>
@@ -2659,7 +2708,7 @@
     </row>
     <row r="7" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N7">
         <v>70005</v>
@@ -2667,7 +2716,7 @@
     </row>
     <row r="8" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N8">
         <v>70006</v>
@@ -2683,7 +2732,7 @@
     </row>
     <row r="10" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N10">
         <v>70008</v>
@@ -2691,7 +2740,7 @@
     </row>
     <row r="11" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N11">
         <v>70009</v>
@@ -2699,7 +2748,7 @@
     </row>
     <row r="12" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N12">
         <v>70010</v>
@@ -2719,7 +2768,7 @@
     </row>
     <row r="14" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N14">
         <v>70012</v>
@@ -2730,7 +2779,7 @@
         <v>21475</v>
       </c>
       <c r="M15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N15">
         <v>70013</v>
@@ -2738,7 +2787,7 @@
     </row>
     <row r="16" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N16">
         <v>70014</v>
@@ -2746,7 +2795,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N17">
         <v>70015</v>
@@ -2754,7 +2803,7 @@
     </row>
     <row r="18" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N18">
         <v>70016</v>
@@ -2762,7 +2811,7 @@
     </row>
     <row r="19" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N19">
         <v>70017</v>
@@ -2770,7 +2819,7 @@
     </row>
     <row r="20" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N20">
         <v>70018</v>
@@ -2778,7 +2827,7 @@
     </row>
     <row r="21" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N21">
         <v>70019</v>
@@ -2810,7 +2859,7 @@
     </row>
     <row r="25" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N25">
         <v>70023</v>
@@ -2818,7 +2867,7 @@
     </row>
     <row r="26" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N26">
         <v>70024</v>
@@ -2826,7 +2875,7 @@
     </row>
     <row r="27" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N27">
         <v>70025</v>
@@ -2834,7 +2883,7 @@
     </row>
     <row r="28" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>70026</v>
@@ -2842,7 +2891,7 @@
     </row>
     <row r="29" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N29">
         <v>70027</v>
@@ -2850,7 +2899,7 @@
     </row>
     <row r="30" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N30">
         <v>70028</v>
@@ -2858,7 +2907,7 @@
     </row>
     <row r="31" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N31">
         <v>70029</v>
@@ -2874,7 +2923,7 @@
     </row>
     <row r="33" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N33">
         <v>70031</v>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="164">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -146,10 +146,6 @@
   </si>
   <si>
     <t>饮食店的姐妹花姐姐，做事情很认真，是饮食店的看板娘。</t>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>布蓝达</t>
@@ -951,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:N42"/>
+  <dimension ref="A2:N41"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -993,19 +989,19 @@
         <v>29</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1037,19 +1033,19 @@
         <v>30</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="L3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1057,7 +1053,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1078,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L4" s="2">
         <v>8001</v>
@@ -1090,7 +1086,7 @@
         <v>8001</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -1125,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1154,14 +1150,14 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="L6" s="2">
         <v>8001</v>
       </c>
@@ -1169,7 +1165,7 @@
         <v>8001</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1198,14 +1194,14 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="L7" s="2">
         <v>8001</v>
       </c>
@@ -1213,7 +1209,7 @@
         <v>8001</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1221,7 +1217,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -1242,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L8" s="2">
         <v>8001</v>
@@ -1257,7 +1253,7 @@
         <v>8001</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1265,7 +1261,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -1286,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L9" s="2">
         <v>8001</v>
@@ -1301,7 +1297,7 @@
         <v>8001</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1309,7 +1305,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -1330,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L10" s="2">
         <v>8001</v>
@@ -1342,7 +1338,7 @@
         <v>8001</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1350,7 +1346,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -1371,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L11" s="2">
         <v>8001</v>
@@ -1383,7 +1379,7 @@
         <v>8001</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1412,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L12" s="2">
         <v>8001</v>
@@ -1421,7 +1417,7 @@
         <v>8001</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1429,7 +1425,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1">
         <v>12</v>
@@ -1450,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L13" s="2">
         <v>8001</v>
@@ -1462,7 +1458,7 @@
         <v>8001</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1491,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L14" s="2">
         <v>8001</v>
@@ -1500,7 +1496,7 @@
         <v>8001</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1532,10 +1528,10 @@
         <v>31</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L15" s="2">
         <v>8001</v>
@@ -1544,7 +1540,7 @@
         <v>8001</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1573,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L16" s="2">
         <v>8001</v>
@@ -1582,7 +1578,7 @@
         <v>8001</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1614,10 +1610,10 @@
         <v>33</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L17" s="2">
         <v>8001</v>
@@ -1626,7 +1622,7 @@
         <v>8001</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1634,7 +1630,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1">
         <v>17</v>
@@ -1655,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L18" s="2">
         <v>8001</v>
@@ -1667,7 +1663,7 @@
         <v>8001</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1696,10 +1692,10 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L19" s="2">
         <v>8001</v>
@@ -1708,7 +1704,7 @@
         <v>8001</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1716,7 +1712,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1">
         <v>19</v>
@@ -1737,13 +1733,13 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L20" s="2">
         <v>8001</v>
@@ -1752,18 +1748,18 @@
         <v>8001</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>20</v>
+      <c r="A21" s="5">
+        <v>21</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="1">
-        <v>20</v>
+      <c r="C21" s="5">
+        <v>21</v>
       </c>
       <c r="D21" s="1" t="b">
         <v>1</v>
@@ -1781,10 +1777,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L21" s="2">
         <v>8001</v>
@@ -1793,18 +1789,18 @@
         <v>8001</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
-        <v>21</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>22</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="5">
-        <v>21</v>
+        <v>44</v>
+      </c>
+      <c r="C22" s="1">
+        <v>22</v>
       </c>
       <c r="D22" s="1" t="b">
         <v>1</v>
@@ -1825,7 +1821,10 @@
         <v>83</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="L22" s="2">
         <v>8001</v>
@@ -1837,15 +1836,15 @@
         <v>138</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>22</v>
+    <row r="23" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="5">
+        <v>23</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C23" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="1" t="b">
         <v>1</v>
@@ -1863,13 +1862,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="L23" s="2">
         <v>8001</v>
@@ -1881,15 +1877,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C24" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D24" s="1" t="b">
         <v>1</v>
@@ -1907,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L24" s="2">
         <v>8001</v>
@@ -1922,15 +1918,15 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
-        <v>24</v>
+    <row r="25" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>25</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C25" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1" t="b">
         <v>1</v>
@@ -1948,10 +1944,13 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="L25" s="2">
         <v>8001</v>
@@ -1963,15 +1962,15 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>25</v>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="5">
+        <v>26</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C26" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" s="1" t="b">
         <v>1</v>
@@ -1989,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>163</v>
@@ -2009,13 +2008,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27" s="1" t="b">
         <v>1</v>
@@ -2036,10 +2035,7 @@
         <v>91</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="L27" s="2">
         <v>8001</v>
@@ -2051,15 +2047,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C28" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" s="1" t="b">
         <v>1</v>
@@ -2080,7 +2076,7 @@
         <v>92</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L28" s="2">
         <v>8001</v>
@@ -2094,13 +2090,13 @@
     </row>
     <row r="29" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1" t="b">
         <v>1</v>
@@ -2121,7 +2117,7 @@
         <v>93</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L29" s="2">
         <v>8001</v>
@@ -2135,13 +2131,13 @@
     </row>
     <row r="30" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D30" s="1" t="b">
         <v>1</v>
@@ -2159,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L30" s="2">
         <v>8001</v>
@@ -2176,13 +2172,13 @@
     </row>
     <row r="31" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C31" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D31" s="1" t="b">
         <v>1</v>
@@ -2200,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L31" s="2">
         <v>8001</v>
@@ -2215,18 +2211,18 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="5">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>53</v>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
+        <v>32</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C32" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D32" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2238,13 +2234,10 @@
         <v>1</v>
       </c>
       <c r="H32" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L32" s="2">
         <v>8001</v>
@@ -2253,18 +2246,18 @@
         <v>8001</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D33" s="1" t="b">
         <v>0</v>
@@ -2282,7 +2275,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L33" s="2">
         <v>8001</v>
@@ -2291,21 +2284,21 @@
         <v>8001</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
-        <v>33</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>24</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>34</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C34" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D34" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -2317,10 +2310,13 @@
         <v>1</v>
       </c>
       <c r="H34" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L34" s="2">
         <v>8001</v>
@@ -2329,18 +2325,18 @@
         <v>8001</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
-        <v>34</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="5">
+        <v>35</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C35" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D35" s="1" t="b">
         <v>1</v>
@@ -2358,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L35" s="2">
         <v>8001</v>
@@ -2373,15 +2369,15 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="5">
-        <v>35</v>
+    <row r="36" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>36</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C36" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D36" s="1" t="b">
         <v>1</v>
@@ -2399,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="L36" s="2">
         <v>8001</v>
@@ -2414,15 +2410,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <v>36</v>
+    <row r="37" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A37" s="5">
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C37" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D37" s="1" t="b">
         <v>1</v>
@@ -2442,8 +2438,8 @@
       <c r="I37" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>159</v>
+      <c r="K37" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="L37" s="2">
         <v>8001</v>
@@ -2455,15 +2451,15 @@
         <v>151</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C38" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D38" s="1" t="b">
         <v>1</v>
@@ -2481,10 +2477,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="L38" s="2">
         <v>8001</v>
@@ -2497,14 +2490,14 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="5">
-        <v>38</v>
+      <c r="A39" s="1">
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C39" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1" t="b">
         <v>1</v>
@@ -2522,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L39" s="2">
         <v>8001</v>
@@ -2535,14 +2528,14 @@
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
-        <v>39</v>
+      <c r="A40" s="5">
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C40" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D40" s="1" t="b">
         <v>1</v>
@@ -2560,7 +2553,10 @@
         <v>0</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>75</v>
+        <v>34</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="L40" s="2">
         <v>8001</v>
@@ -2573,14 +2569,14 @@
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A41" s="5">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>25</v>
+      <c r="A41" s="1">
+        <v>41</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="C41" s="1">
-        <v>40</v>
+        <v>213</v>
       </c>
       <c r="D41" s="1" t="b">
         <v>1</v>
@@ -2598,10 +2594,10 @@
         <v>0</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>159</v>
+        <v>96</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="L41" s="2">
         <v>8001</v>
@@ -2610,48 +2606,7 @@
         <v>8001</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C42" s="1">
-        <v>213</v>
-      </c>
-      <c r="D42" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1">
-        <v>0</v>
-      </c>
-      <c r="G42" s="1">
-        <v>1</v>
-      </c>
-      <c r="H42" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="L42" s="2">
-        <v>8001</v>
-      </c>
-      <c r="M42" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2671,12 +2626,12 @@
   <sheetData>
     <row r="2" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N3">
         <v>70001</v>
@@ -2684,7 +2639,7 @@
     </row>
     <row r="4" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N4">
         <v>70002</v>
@@ -2692,7 +2647,7 @@
     </row>
     <row r="5" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N5">
         <v>70003</v>
@@ -2700,7 +2655,7 @@
     </row>
     <row r="6" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N6">
         <v>70004</v>
@@ -2708,7 +2663,7 @@
     </row>
     <row r="7" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N7">
         <v>70005</v>
@@ -2716,7 +2671,7 @@
     </row>
     <row r="8" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N8">
         <v>70006</v>
@@ -2732,7 +2687,7 @@
     </row>
     <row r="10" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N10">
         <v>70008</v>
@@ -2740,7 +2695,7 @@
     </row>
     <row r="11" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N11">
         <v>70009</v>
@@ -2748,7 +2703,7 @@
     </row>
     <row r="12" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N12">
         <v>70010</v>
@@ -2768,7 +2723,7 @@
     </row>
     <row r="14" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N14">
         <v>70012</v>
@@ -2779,7 +2734,7 @@
         <v>21475</v>
       </c>
       <c r="M15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N15">
         <v>70013</v>
@@ -2787,7 +2742,7 @@
     </row>
     <row r="16" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N16">
         <v>70014</v>
@@ -2795,7 +2750,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N17">
         <v>70015</v>
@@ -2803,7 +2758,7 @@
     </row>
     <row r="18" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N18">
         <v>70016</v>
@@ -2811,7 +2766,7 @@
     </row>
     <row r="19" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N19">
         <v>70017</v>
@@ -2819,7 +2774,7 @@
     </row>
     <row r="20" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N20">
         <v>70018</v>
@@ -2827,7 +2782,7 @@
     </row>
     <row r="21" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N21">
         <v>70019</v>
@@ -2859,7 +2814,7 @@
     </row>
     <row r="25" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N25">
         <v>70023</v>
@@ -2867,7 +2822,7 @@
     </row>
     <row r="26" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N26">
         <v>70024</v>
@@ -2875,7 +2830,7 @@
     </row>
     <row r="27" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N27">
         <v>70025</v>
@@ -2883,7 +2838,7 @@
     </row>
     <row r="28" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N28">
         <v>70026</v>
@@ -2891,7 +2846,7 @@
     </row>
     <row r="29" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N29">
         <v>70027</v>
@@ -2899,7 +2854,7 @@
     </row>
     <row r="30" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N30">
         <v>70028</v>
@@ -2907,7 +2862,7 @@
     </row>
     <row r="31" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N31">
         <v>70029</v>
@@ -2923,7 +2878,7 @@
     </row>
     <row r="33" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N33">
         <v>70031</v>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -387,9 +387,6 @@
     <t>talkForFriendShip</t>
   </si>
   <si>
-    <t>List&lt;int2&gt;</t>
-  </si>
-  <si>
     <t>地点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -463,106 +460,6 @@
     <t>纺织婆婆</t>
   </si>
   <si>
-    <t>0,70032</t>
-  </si>
-  <si>
-    <t>0,70002</t>
-  </si>
-  <si>
-    <t>0,70001</t>
-  </si>
-  <si>
-    <t>0,70003</t>
-  </si>
-  <si>
-    <t>0,70004</t>
-  </si>
-  <si>
-    <t>0,70005</t>
-  </si>
-  <si>
-    <t>0,70006</t>
-  </si>
-  <si>
-    <t>0,70007</t>
-  </si>
-  <si>
-    <t>0,70008</t>
-  </si>
-  <si>
-    <t>0,70009</t>
-  </si>
-  <si>
-    <t>0,70010</t>
-  </si>
-  <si>
-    <t>0,70011</t>
-  </si>
-  <si>
-    <t>0,70012</t>
-  </si>
-  <si>
-    <t>0,70013</t>
-  </si>
-  <si>
-    <t>0,70014</t>
-  </si>
-  <si>
-    <t>0,70015</t>
-  </si>
-  <si>
-    <t>0,70016</t>
-  </si>
-  <si>
-    <t>0,70017</t>
-  </si>
-  <si>
-    <t>0,70018</t>
-  </si>
-  <si>
-    <t>0,70019</t>
-  </si>
-  <si>
-    <t>0,70020</t>
-  </si>
-  <si>
-    <t>0,70021</t>
-  </si>
-  <si>
-    <t>0,70022</t>
-  </si>
-  <si>
-    <t>0,70023</t>
-  </si>
-  <si>
-    <t>0,70024</t>
-  </si>
-  <si>
-    <t>0,70025</t>
-  </si>
-  <si>
-    <t>0,70026</t>
-  </si>
-  <si>
-    <t>0,70027</t>
-  </si>
-  <si>
-    <t>0,70028</t>
-  </si>
-  <si>
-    <t>0,70029</t>
-  </si>
-  <si>
-    <t>0,70030</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>0,70031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>艾德文娜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -587,6 +484,109 @@
   <si>
     <t>鱼店</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int3&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,70032</t>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>0,0,70002</t>
+  </si>
+  <si>
+    <t>0,0,70001</t>
+  </si>
+  <si>
+    <t>0,0,70003</t>
+  </si>
+  <si>
+    <t>0,0,70004</t>
+  </si>
+  <si>
+    <t>0,0,70005</t>
+  </si>
+  <si>
+    <t>0,0,70006</t>
+  </si>
+  <si>
+    <t>0,0,70007</t>
+  </si>
+  <si>
+    <t>0,0,70008</t>
+  </si>
+  <si>
+    <t>0,0,70009</t>
+  </si>
+  <si>
+    <t>0,0,70010</t>
+  </si>
+  <si>
+    <t>0,0,70011</t>
+  </si>
+  <si>
+    <t>0,0,70012</t>
+  </si>
+  <si>
+    <t>0,0,70013</t>
+  </si>
+  <si>
+    <t>0,0,70014</t>
+  </si>
+  <si>
+    <t>0,0,70015</t>
+  </si>
+  <si>
+    <t>0,0,70016</t>
+  </si>
+  <si>
+    <t>0,0,70017</t>
+  </si>
+  <si>
+    <t>0,0,70018</t>
+  </si>
+  <si>
+    <t>0,0,70019</t>
+  </si>
+  <si>
+    <t>0,0,70020</t>
+  </si>
+  <si>
+    <t>0,0,70021</t>
+  </si>
+  <si>
+    <t>0,0,70022</t>
+  </si>
+  <si>
+    <t>0,0,70023</t>
+  </si>
+  <si>
+    <t>0,0,70024</t>
+  </si>
+  <si>
+    <t>0,0,70025</t>
+  </si>
+  <si>
+    <t>0,0,70026</t>
+  </si>
+  <si>
+    <t>0,0,70027</t>
+  </si>
+  <si>
+    <t>0,0,70028</t>
+  </si>
+  <si>
+    <t>0,0,70029</t>
+  </si>
+  <si>
+    <t>0,0,70030</t>
+  </si>
+  <si>
+    <t>0,0,70031</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1001,7 @@
         <v>62</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1086,7 +1086,7 @@
         <v>8001</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1165,7 +1165,7 @@
         <v>8001</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1209,7 +1209,7 @@
         <v>8001</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1253,7 +1253,7 @@
         <v>8001</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1297,7 +1297,7 @@
         <v>8001</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1338,7 +1338,7 @@
         <v>8001</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1379,7 +1379,7 @@
         <v>8001</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1417,7 +1417,7 @@
         <v>8001</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1458,7 +1458,7 @@
         <v>8001</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1496,7 +1496,7 @@
         <v>8001</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1540,7 +1540,7 @@
         <v>8001</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1578,7 +1578,7 @@
         <v>8001</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1613,7 +1613,7 @@
         <v>57</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="L17" s="2">
         <v>8001</v>
@@ -1622,7 +1622,7 @@
         <v>8001</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1663,7 +1663,7 @@
         <v>8001</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1704,7 +1704,7 @@
         <v>8001</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1739,7 +1739,7 @@
         <v>57</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="L20" s="2">
         <v>8001</v>
@@ -1748,7 +1748,7 @@
         <v>8001</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1789,7 +1789,7 @@
         <v>8001</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1824,7 +1824,7 @@
         <v>57</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="L22" s="2">
         <v>8001</v>
@@ -1833,7 +1833,7 @@
         <v>8001</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1874,7 +1874,7 @@
         <v>8001</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -1915,7 +1915,7 @@
         <v>8001</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1950,7 +1950,7 @@
         <v>57</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="L25" s="2">
         <v>8001</v>
@@ -1959,7 +1959,7 @@
         <v>8001</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -1994,7 +1994,7 @@
         <v>57</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="L26" s="2">
         <v>8001</v>
@@ -2003,7 +2003,7 @@
         <v>8001</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -2044,7 +2044,7 @@
         <v>8001</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2085,7 +2085,7 @@
         <v>8001</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2126,7 +2126,7 @@
         <v>8001</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2167,7 +2167,7 @@
         <v>8001</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2208,7 +2208,7 @@
         <v>8001</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -2246,7 +2246,7 @@
         <v>8001</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -2284,7 +2284,7 @@
         <v>8001</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2325,7 +2325,7 @@
         <v>8001</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2366,7 +2366,7 @@
         <v>8001</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2398,16 +2398,16 @@
         <v>75</v>
       </c>
       <c r="K36" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L36" s="2">
+        <v>8001</v>
+      </c>
+      <c r="M36" s="2">
+        <v>8001</v>
+      </c>
+      <c r="N36" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="L36" s="2">
-        <v>8001</v>
-      </c>
-      <c r="M36" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -2439,7 +2439,7 @@
         <v>76</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="L37" s="2">
         <v>8001</v>
@@ -2448,7 +2448,7 @@
         <v>8001</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2486,7 +2486,7 @@
         <v>8001</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2524,7 +2524,7 @@
         <v>8001</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2556,7 +2556,7 @@
         <v>34</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="L40" s="2">
         <v>8001</v>
@@ -2565,7 +2565,7 @@
         <v>8001</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2573,7 +2573,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="C41" s="1">
         <v>213</v>
@@ -2597,7 +2597,7 @@
         <v>96</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="L41" s="2">
         <v>8001</v>
@@ -2606,7 +2606,7 @@
         <v>8001</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2626,12 +2626,12 @@
   <sheetData>
     <row r="2" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N3">
         <v>70001</v>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="4" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N4">
         <v>70002</v>
@@ -2663,7 +2663,7 @@
     </row>
     <row r="7" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7">
         <v>70005</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="8" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N8">
         <v>70006</v>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="10" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10">
         <v>70008</v>
@@ -2695,7 +2695,7 @@
     </row>
     <row r="11" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N11">
         <v>70009</v>
@@ -2703,7 +2703,7 @@
     </row>
     <row r="12" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N12">
         <v>70010</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="14" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N14">
         <v>70012</v>
@@ -2734,7 +2734,7 @@
         <v>21475</v>
       </c>
       <c r="M15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N15">
         <v>70013</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="16" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N16">
         <v>70014</v>
@@ -2750,7 +2750,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N17">
         <v>70015</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="18" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N18">
         <v>70016</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="19" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N19">
         <v>70017</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="20" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N20">
         <v>70018</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="21" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N21">
         <v>70019</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="25" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N25">
         <v>70023</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="26" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N26">
         <v>70024</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="27" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N27">
         <v>70025</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="28" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N28">
         <v>70026</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="29" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N29">
         <v>70027</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="30" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N30">
         <v>70028</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="31" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N31">
         <v>70029</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="33" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N33">
         <v>70031</v>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="165">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -587,6 +587,10 @@
   </si>
   <si>
     <t>0,0,70031</t>
+  </si>
+  <si>
+    <t>1,2,4,12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1449,7 +1453,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>57</v>
+        <v>164</v>
       </c>
       <c r="L13" s="2">
         <v>8001</v>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -380,10 +380,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>talkForFriendShip</t>
   </si>
   <si>
@@ -591,6 +587,10 @@
   <si>
     <t>1,2,4,12</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1005,7 +1005,7 @@
         <v>62</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1049,7 +1049,7 @@
         <v>64</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1057,7 +1057,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1090,7 +1090,7 @@
         <v>8001</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1169,7 +1169,7 @@
         <v>8001</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1213,7 +1213,7 @@
         <v>8001</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1257,7 +1257,7 @@
         <v>8001</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1301,7 +1301,7 @@
         <v>8001</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1342,7 +1342,7 @@
         <v>8001</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1383,7 +1383,7 @@
         <v>8001</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1421,7 +1421,7 @@
         <v>8001</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1453,7 +1453,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L13" s="2">
         <v>8001</v>
@@ -1462,7 +1462,7 @@
         <v>8001</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1500,7 +1500,7 @@
         <v>8001</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1544,7 +1544,7 @@
         <v>8001</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1582,7 +1582,7 @@
         <v>8001</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1617,7 +1617,7 @@
         <v>57</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L17" s="2">
         <v>8001</v>
@@ -1626,7 +1626,7 @@
         <v>8001</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1667,7 +1667,7 @@
         <v>8001</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1708,7 +1708,7 @@
         <v>8001</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1743,7 +1743,7 @@
         <v>57</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L20" s="2">
         <v>8001</v>
@@ -1752,7 +1752,7 @@
         <v>8001</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1793,7 +1793,7 @@
         <v>8001</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -1828,7 +1828,7 @@
         <v>57</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L22" s="2">
         <v>8001</v>
@@ -1837,7 +1837,7 @@
         <v>8001</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1878,7 +1878,7 @@
         <v>8001</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -1919,7 +1919,7 @@
         <v>8001</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -1954,7 +1954,7 @@
         <v>57</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L25" s="2">
         <v>8001</v>
@@ -1963,7 +1963,7 @@
         <v>8001</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -1998,7 +1998,7 @@
         <v>57</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L26" s="2">
         <v>8001</v>
@@ -2007,7 +2007,7 @@
         <v>8001</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -2048,7 +2048,7 @@
         <v>8001</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2089,7 +2089,7 @@
         <v>8001</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2130,7 +2130,7 @@
         <v>8001</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2171,7 +2171,7 @@
         <v>8001</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2212,7 +2212,7 @@
         <v>8001</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -2250,7 +2250,7 @@
         <v>8001</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -2288,7 +2288,7 @@
         <v>8001</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2329,7 +2329,7 @@
         <v>8001</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2370,7 +2370,7 @@
         <v>8001</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2402,7 +2402,7 @@
         <v>75</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L36" s="2">
         <v>8001</v>
@@ -2411,7 +2411,7 @@
         <v>8001</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
@@ -2443,7 +2443,7 @@
         <v>76</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L37" s="2">
         <v>8001</v>
@@ -2452,7 +2452,7 @@
         <v>8001</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2490,7 +2490,7 @@
         <v>8001</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2528,7 +2528,7 @@
         <v>8001</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2560,7 +2560,7 @@
         <v>34</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L40" s="2">
         <v>8001</v>
@@ -2569,7 +2569,7 @@
         <v>8001</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2577,7 +2577,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C41" s="1">
         <v>213</v>
@@ -2601,7 +2601,7 @@
         <v>96</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L41" s="2">
         <v>8001</v>
@@ -2610,7 +2610,7 @@
         <v>8001</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2630,12 +2630,12 @@
   <sheetData>
     <row r="2" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N3">
         <v>70001</v>
@@ -2643,7 +2643,7 @@
     </row>
     <row r="4" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>70002</v>
@@ -2667,7 +2667,7 @@
     </row>
     <row r="7" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N7">
         <v>70005</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="8" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N8">
         <v>70006</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="10" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N10">
         <v>70008</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="11" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N11">
         <v>70009</v>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="12" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N12">
         <v>70010</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="14" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N14">
         <v>70012</v>
@@ -2738,7 +2738,7 @@
         <v>21475</v>
       </c>
       <c r="M15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N15">
         <v>70013</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="16" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N16">
         <v>70014</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N17">
         <v>70015</v>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="18" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N18">
         <v>70016</v>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="19" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N19">
         <v>70017</v>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="20" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N20">
         <v>70018</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="21" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N21">
         <v>70019</v>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="25" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N25">
         <v>70023</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="26" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N26">
         <v>70024</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="27" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N27">
         <v>70025</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="28" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N28">
         <v>70026</v>
@@ -2850,7 +2850,7 @@
     </row>
     <row r="29" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N29">
         <v>70027</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="30" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N30">
         <v>70028</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="31" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N31">
         <v>70029</v>
@@ -2882,7 +2882,7 @@
     </row>
     <row r="33" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N33">
         <v>70031</v>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="171">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -590,6 +590,30 @@
   </si>
   <si>
     <t>班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0,8,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>friendLevels</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -951,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:N41"/>
+  <dimension ref="A2:O41"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
@@ -960,11 +984,11 @@
     <col min="6" max="7" width="15.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.5" style="1"/>
     <col min="9" max="9" width="40.25" style="1" customWidth="1"/>
-    <col min="10" max="11" width="9.5" style="2"/>
-    <col min="12" max="16384" width="9.5" style="1"/>
+    <col min="10" max="12" width="9.5" style="2"/>
+    <col min="13" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -996,19 +1020,22 @@
         <v>54</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1040,19 +1067,22 @@
         <v>55</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1083,17 +1113,20 @@
       <c r="J4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L4" s="2">
-        <v>8001</v>
+      <c r="K4" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M4" s="2">
         <v>8001</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1118,17 +1151,20 @@
       <c r="H5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L5" s="2">
-        <v>0</v>
+      <c r="K5" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M5" s="2">
         <v>0</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1160,19 +1196,22 @@
         <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L6" s="2">
-        <v>8001</v>
-      </c>
       <c r="M6" s="2">
         <v>8001</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1204,19 +1243,22 @@
         <v>57</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L7" s="2">
-        <v>8001</v>
-      </c>
       <c r="M7" s="2">
         <v>8001</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1248,19 +1290,22 @@
         <v>57</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="2">
-        <v>8001</v>
-      </c>
       <c r="M8" s="2">
         <v>8001</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1292,19 +1337,22 @@
         <v>57</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="2">
-        <v>8001</v>
-      </c>
       <c r="M9" s="2">
         <v>8001</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1335,17 +1383,20 @@
       <c r="J10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L10" s="2">
-        <v>8001</v>
+      <c r="K10" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M10" s="2">
         <v>8001</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1376,17 +1427,20 @@
       <c r="J11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="2">
-        <v>8001</v>
+      <c r="K11" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="M11" s="2">
         <v>8001</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N11" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1414,17 +1468,20 @@
       <c r="J12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="2">
-        <v>8001</v>
+      <c r="K12" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M12" s="2">
         <v>8001</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="N12" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1455,17 +1512,20 @@
       <c r="J13" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="L13" s="2">
-        <v>8001</v>
+      <c r="K13" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="M13" s="2">
         <v>8001</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="N13" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1493,17 +1553,20 @@
       <c r="J14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L14" s="2">
-        <v>8001</v>
+      <c r="K14" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M14" s="2">
         <v>8001</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="N14" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1535,19 +1598,22 @@
         <v>57</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="2">
-        <v>8001</v>
-      </c>
       <c r="M15" s="2">
         <v>8001</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="N15" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1575,17 +1641,20 @@
       <c r="J16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L16" s="2">
-        <v>8001</v>
+      <c r="K16" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M16" s="2">
         <v>8001</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N16" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1617,19 +1686,22 @@
         <v>57</v>
       </c>
       <c r="K17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L17" s="2">
-        <v>8001</v>
-      </c>
       <c r="M17" s="2">
         <v>8001</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="N17" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1660,17 +1732,20 @@
       <c r="J18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L18" s="2">
-        <v>8001</v>
+      <c r="K18" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="M18" s="2">
         <v>8001</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="N18" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1701,17 +1776,20 @@
       <c r="J19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L19" s="2">
-        <v>8001</v>
+      <c r="K19" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="M19" s="2">
         <v>8001</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="N19" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1742,20 +1820,23 @@
       <c r="J20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="L20" s="2">
-        <v>8001</v>
-      </c>
       <c r="M20" s="2">
         <v>8001</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="N20" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>21</v>
       </c>
@@ -1786,17 +1867,20 @@
       <c r="J21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="2">
-        <v>8001</v>
+      <c r="K21" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M21" s="2">
         <v>8001</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N21" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O21" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -1827,20 +1911,23 @@
       <c r="J22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L22" s="2">
-        <v>8001</v>
-      </c>
       <c r="M22" s="2">
         <v>8001</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="N22" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>23</v>
       </c>
@@ -1871,17 +1958,20 @@
       <c r="J23" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L23" s="2">
-        <v>8001</v>
+      <c r="K23" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M23" s="2">
         <v>8001</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N23" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>24</v>
       </c>
@@ -1912,17 +2002,20 @@
       <c r="J24" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L24" s="2">
-        <v>8001</v>
+      <c r="K24" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="M24" s="2">
         <v>8001</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="N24" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -1953,20 +2046,23 @@
       <c r="J25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L25" s="2">
-        <v>8001</v>
-      </c>
       <c r="M25" s="2">
         <v>8001</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N25" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>26</v>
       </c>
@@ -1997,20 +2093,23 @@
       <c r="J26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="L26" s="2">
-        <v>8001</v>
-      </c>
       <c r="M26" s="2">
         <v>8001</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="N26" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>27</v>
       </c>
@@ -2041,17 +2140,20 @@
       <c r="J27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L27" s="2">
-        <v>8001</v>
+      <c r="K27" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="M27" s="2">
         <v>8001</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="N27" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>28</v>
       </c>
@@ -2082,17 +2184,20 @@
       <c r="J28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L28" s="2">
-        <v>8001</v>
+      <c r="K28" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M28" s="2">
         <v>8001</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="N28" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O28" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>29</v>
       </c>
@@ -2123,17 +2228,20 @@
       <c r="J29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L29" s="2">
-        <v>8001</v>
+      <c r="K29" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="M29" s="2">
         <v>8001</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="N29" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>30</v>
       </c>
@@ -2164,17 +2272,20 @@
       <c r="J30" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L30" s="2">
-        <v>8001</v>
+      <c r="K30" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="M30" s="2">
         <v>8001</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>31</v>
       </c>
@@ -2205,17 +2316,20 @@
       <c r="J31" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L31" s="2">
-        <v>8001</v>
+      <c r="K31" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M31" s="2">
         <v>8001</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="N31" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>32</v>
       </c>
@@ -2243,17 +2357,20 @@
       <c r="J32" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="2">
-        <v>8001</v>
+      <c r="K32" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M32" s="2">
         <v>8001</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="N32" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>33</v>
       </c>
@@ -2281,17 +2398,20 @@
       <c r="J33" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L33" s="2">
-        <v>8001</v>
+      <c r="K33" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M33" s="2">
         <v>8001</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="N33" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -2322,17 +2442,20 @@
       <c r="J34" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L34" s="2">
-        <v>8001</v>
+      <c r="K34" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M34" s="2">
         <v>8001</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="N34" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>35</v>
       </c>
@@ -2363,17 +2486,20 @@
       <c r="J35" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L35" s="2">
-        <v>8001</v>
+      <c r="K35" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="M35" s="2">
         <v>8001</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="N35" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -2401,20 +2527,26 @@
       <c r="I36" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="J36" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="K36" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L36" s="2">
-        <v>8001</v>
-      </c>
       <c r="M36" s="2">
         <v>8001</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="N36" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>37</v>
       </c>
@@ -2442,20 +2574,26 @@
       <c r="I37" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="J37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="L37" s="2">
-        <v>8001</v>
-      </c>
       <c r="M37" s="2">
         <v>8001</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="N37" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>38</v>
       </c>
@@ -2483,17 +2621,23 @@
       <c r="I38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L38" s="2">
-        <v>8001</v>
+      <c r="J38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="M38" s="2">
         <v>8001</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="N38" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -2521,17 +2665,23 @@
       <c r="I39" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L39" s="2">
-        <v>8001</v>
+      <c r="J39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="M39" s="2">
         <v>8001</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="N39" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O39" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>40</v>
       </c>
@@ -2559,20 +2709,26 @@
       <c r="I40" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="J40" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="K40" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L40" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L40" s="2">
-        <v>8001</v>
-      </c>
       <c r="M40" s="2">
         <v>8001</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="N40" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O40" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -2600,16 +2756,22 @@
       <c r="I41" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="J41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L41" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L41" s="2">
-        <v>8001</v>
-      </c>
       <c r="M41" s="2">
         <v>8001</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="N41" s="2">
+        <v>8001</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>162</v>
       </c>
     </row>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NPCData!$A$3:$R$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$M$2:$N$2</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="174">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -208,10 +209,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>管家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>亚度尼斯</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -614,6 +611,19 @@
   </si>
   <si>
     <t>friendLevels</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>teamFriendShip</t>
+  </si>
+  <si>
+    <t>failTeamTalk</t>
+  </si>
+  <si>
+    <t>failLoveTalk</t>
+  </si>
+  <si>
+    <t>没落贵族的管家，不离不弃的看护着贵族家族中唯一的继承人。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -975,20 +985,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:O41"/>
+  <dimension ref="A2:R41"/>
   <sheetFormatPr defaultColWidth="9.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.5" style="1"/>
     <col min="3" max="4" width="15.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="7" width="15.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="1"/>
-    <col min="9" max="9" width="40.25" style="1" customWidth="1"/>
-    <col min="10" max="12" width="9.5" style="2"/>
-    <col min="13" max="16384" width="9.5" style="1"/>
+    <col min="8" max="11" width="9.5" style="1"/>
+    <col min="12" max="12" width="40.25" style="1" customWidth="1"/>
+    <col min="13" max="15" width="9.5" style="2"/>
+    <col min="16" max="16384" width="9.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1014,28 +1024,37 @@
         <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1061,33 +1080,42 @@
         <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="M3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="P3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="R3" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1107,26 +1135,35 @@
       <c r="H4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M4" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N4" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P4" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1151,20 +1188,29 @@
       <c r="H5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1189,29 +1235,38 @@
       <c r="H6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M6" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N6" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="P6" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1236,34 +1291,43 @@
       <c r="H7" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N7" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="P7" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -1283,34 +1347,43 @@
       <c r="H8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N8" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I8" s="1">
+        <v>3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>5006</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -1330,34 +1403,43 @@
       <c r="H9" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N9" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -1377,26 +1459,35 @@
       <c r="H10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M10" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N10" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P10" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1421,26 +1512,35 @@
       <c r="H11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M11" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N11" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P11" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1465,23 +1565,32 @@
       <c r="H12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M12" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N12" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P12" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1506,26 +1615,35 @@
       <c r="H13" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="M13" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N13" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="I13" s="1">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2">
+        <v>5007</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="P13" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1550,23 +1668,32 @@
       <c r="H14" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M14" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P14" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1591,29 +1718,38 @@
       <c r="H15" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="1">
+        <v>4</v>
+      </c>
+      <c r="J15" s="2">
+        <v>5008</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M15" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N15" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="P15" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1638,23 +1774,32 @@
       <c r="H16" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M16" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N16" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P16" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1679,29 +1824,38 @@
       <c r="H17" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="1">
+        <v>4</v>
+      </c>
+      <c r="J17" s="2">
+        <v>5009</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="M17" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N17" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P17" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1726,26 +1880,35 @@
       <c r="H18" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M18" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N18" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I18" s="1">
+        <v>4</v>
+      </c>
+      <c r="J18" s="2">
+        <v>5010</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P18" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1770,26 +1933,35 @@
       <c r="H19" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M19" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N19" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="I19" s="1">
+        <v>4</v>
+      </c>
+      <c r="J19" s="1">
+        <v>5011</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P19" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1814,29 +1986,38 @@
       <c r="H20" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>165</v>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M20" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N20" s="2">
-        <v>8001</v>
+        <v>76</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="P20" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>21</v>
       </c>
@@ -1861,26 +2042,35 @@
       <c r="H21" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M21" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N21" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P21" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -1905,29 +2095,38 @@
       <c r="H22" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>165</v>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="M22" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N22" s="2">
-        <v>8001</v>
+        <v>82</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+      <c r="P22" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>23</v>
       </c>
@@ -1952,26 +2151,35 @@
       <c r="H23" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M23" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N23" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P23" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>24</v>
       </c>
@@ -1996,26 +2204,35 @@
       <c r="H24" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="M24" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N24" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I24" s="1">
+        <v>4</v>
+      </c>
+      <c r="J24" s="1">
+        <v>5012</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="P24" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -2040,29 +2257,38 @@
       <c r="H25" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>167</v>
+      <c r="I25" s="1">
+        <v>4</v>
+      </c>
+      <c r="J25" s="1">
+        <v>5013</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="M25" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N25" s="2">
-        <v>8001</v>
+        <v>79</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+      <c r="P25" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>26</v>
       </c>
@@ -2087,29 +2313,38 @@
       <c r="H26" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>165</v>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="M26" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N26" s="2">
-        <v>8001</v>
+        <v>89</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+      <c r="P26" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>27</v>
       </c>
@@ -2134,26 +2369,35 @@
       <c r="H27" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M27" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N27" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I27" s="1">
+        <v>4</v>
+      </c>
+      <c r="J27" s="1">
+        <v>5014</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P27" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>28</v>
       </c>
@@ -2178,26 +2422,35 @@
       <c r="H28" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M28" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N28" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P28" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>29</v>
       </c>
@@ -2222,26 +2475,35 @@
       <c r="H29" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M29" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N29" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I29" s="1">
+        <v>4</v>
+      </c>
+      <c r="J29" s="1">
+        <v>5015</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P29" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>30</v>
       </c>
@@ -2266,31 +2528,40 @@
       <c r="H30" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M30" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N30" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I30" s="1">
+        <v>4</v>
+      </c>
+      <c r="J30" s="1">
+        <v>5016</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P30" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>31</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1">
         <v>31</v>
@@ -2310,26 +2581,35 @@
       <c r="H31" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M31" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N31" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P31" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>32</v>
       </c>
@@ -2354,23 +2634,32 @@
       <c r="H32" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M32" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N32" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P32" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>33</v>
       </c>
@@ -2395,23 +2684,32 @@
       <c r="H33" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J33" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M33" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N33" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P33" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -2436,26 +2734,35 @@
       <c r="H34" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M34" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N34" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P34" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>35</v>
       </c>
@@ -2480,26 +2787,35 @@
       <c r="H35" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M35" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N35" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I35" s="1">
+        <v>4</v>
+      </c>
+      <c r="J35" s="1">
+        <v>5017</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P35" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -2524,29 +2840,38 @@
       <c r="H36" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="M36" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N36" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="I36" s="1">
+        <v>4</v>
+      </c>
+      <c r="J36" s="1">
+        <v>5018</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P36" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>37</v>
       </c>
@@ -2571,29 +2896,38 @@
       <c r="H37" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>165</v>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="M37" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N37" s="2">
-        <v>8001</v>
+        <v>75</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="P37" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>38</v>
       </c>
@@ -2618,31 +2952,40 @@
       <c r="H38" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="M38" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N38" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P38" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C39" s="1">
         <v>39</v>
@@ -2662,26 +3005,35 @@
       <c r="H39" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M39" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N39" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I39" s="1">
+        <v>4</v>
+      </c>
+      <c r="J39" s="1">
+        <v>5019</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="P39" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>40</v>
       </c>
@@ -2706,34 +3058,43 @@
       <c r="H40" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="M40" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N40" s="2">
-        <v>8001</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="M40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P40" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C41" s="1">
         <v>213</v>
@@ -2753,29 +3114,39 @@
       <c r="H41" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>167</v>
+      <c r="I41" s="1">
+        <v>4</v>
+      </c>
+      <c r="J41" s="1">
+        <v>5020</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="M41" s="2">
-        <v>8001</v>
-      </c>
-      <c r="N41" s="2">
-        <v>8001</v>
+        <v>95</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>162</v>
+        <v>125</v>
+      </c>
+      <c r="P41" s="2">
+        <v>8001</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>8001</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:R41"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -2792,12 +3163,12 @@
   <sheetData>
     <row r="2" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N3">
         <v>70001</v>
@@ -2805,7 +3176,7 @@
     </row>
     <row r="4" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N4">
         <v>70002</v>
@@ -2813,7 +3184,7 @@
     </row>
     <row r="5" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N5">
         <v>70003</v>
@@ -2821,7 +3192,7 @@
     </row>
     <row r="6" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N6">
         <v>70004</v>
@@ -2829,7 +3200,7 @@
     </row>
     <row r="7" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>70005</v>
@@ -2837,7 +3208,7 @@
     </row>
     <row r="8" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N8">
         <v>70006</v>
@@ -2853,7 +3224,7 @@
     </row>
     <row r="10" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N10">
         <v>70008</v>
@@ -2861,7 +3232,7 @@
     </row>
     <row r="11" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N11">
         <v>70009</v>
@@ -2869,7 +3240,7 @@
     </row>
     <row r="12" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N12">
         <v>70010</v>
@@ -2889,7 +3260,7 @@
     </row>
     <row r="14" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N14">
         <v>70012</v>
@@ -2900,7 +3271,7 @@
         <v>21475</v>
       </c>
       <c r="M15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N15">
         <v>70013</v>
@@ -2908,7 +3279,7 @@
     </row>
     <row r="16" spans="8:14" x14ac:dyDescent="0.2">
       <c r="M16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N16">
         <v>70014</v>
@@ -2916,7 +3287,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N17">
         <v>70015</v>
@@ -2924,7 +3295,7 @@
     </row>
     <row r="18" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N18">
         <v>70016</v>
@@ -2932,7 +3303,7 @@
     </row>
     <row r="19" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N19">
         <v>70017</v>
@@ -2940,7 +3311,7 @@
     </row>
     <row r="20" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N20">
         <v>70018</v>
@@ -2948,7 +3319,7 @@
     </row>
     <row r="21" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N21">
         <v>70019</v>
@@ -2980,7 +3351,7 @@
     </row>
     <row r="25" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N25">
         <v>70023</v>
@@ -2988,7 +3359,7 @@
     </row>
     <row r="26" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N26">
         <v>70024</v>
@@ -2996,7 +3367,7 @@
     </row>
     <row r="27" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N27">
         <v>70025</v>
@@ -3004,7 +3375,7 @@
     </row>
     <row r="28" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N28">
         <v>70026</v>
@@ -3012,7 +3383,7 @@
     </row>
     <row r="29" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N29">
         <v>70027</v>
@@ -3020,7 +3391,7 @@
     </row>
     <row r="30" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N30">
         <v>70028</v>
@@ -3028,7 +3399,7 @@
     </row>
     <row r="31" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N31">
         <v>70029</v>
@@ -3044,7 +3415,7 @@
     </row>
     <row r="33" spans="13:14" x14ac:dyDescent="0.2">
       <c r="M33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N33">
         <v>70031</v>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -3626,7 +3626,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -3679,7 +3679,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -3726,7 +3726,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3782,7 +3782,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3838,7 +3838,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3894,7 +3894,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -3950,7 +3950,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4056,7 +4056,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4109,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="D13" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4165,7 +4165,7 @@
         <v>16</v>
       </c>
       <c r="D14" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -4221,7 +4221,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
@@ -4274,7 +4274,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -4327,7 +4327,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>21</v>
       </c>
       <c r="D18" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -4436,7 +4436,7 @@
         <v>22</v>
       </c>
       <c r="D19" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -4492,7 +4492,7 @@
         <v>23</v>
       </c>
       <c r="D20" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -4545,7 +4545,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -4598,7 +4598,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -4654,7 +4654,7 @@
         <v>26</v>
       </c>
       <c r="D23" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -4710,7 +4710,7 @@
         <v>27</v>
       </c>
       <c r="D24" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -4763,7 +4763,7 @@
         <v>28</v>
       </c>
       <c r="D25" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -4816,7 +4816,7 @@
         <v>29</v>
       </c>
       <c r="D26" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -4869,7 +4869,7 @@
         <v>30</v>
       </c>
       <c r="D27" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -4922,7 +4922,7 @@
         <v>31</v>
       </c>
       <c r="D28" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -4975,7 +4975,7 @@
         <v>34</v>
       </c>
       <c r="D29" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -5028,7 +5028,7 @@
         <v>35</v>
       </c>
       <c r="D30" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5081,7 +5081,7 @@
         <v>36</v>
       </c>
       <c r="D31" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5137,7 +5137,7 @@
         <v>37</v>
       </c>
       <c r="D32" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5193,7 +5193,7 @@
         <v>38</v>
       </c>
       <c r="D33" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -5246,7 +5246,7 @@
         <v>39</v>
       </c>
       <c r="D34" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -5299,7 +5299,7 @@
         <v>40</v>
       </c>
       <c r="D35" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -5355,7 +5355,7 @@
         <v>213</v>
       </c>
       <c r="D36" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>

--- a/Datas/NPCData.xlsx
+++ b/Datas/NPCData.xlsx
@@ -3626,7 +3626,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -3679,7 +3679,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -3726,7 +3726,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3782,7 +3782,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3838,7 +3838,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3894,7 +3894,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -3950,7 +3950,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -4056,7 +4056,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -4109,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="D13" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4165,7 +4165,7 @@
         <v>16</v>
       </c>
       <c r="D14" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -4221,7 +4221,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
@@ -4274,7 +4274,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -4327,7 +4327,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>21</v>
       </c>
       <c r="D18" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -4436,7 +4436,7 @@
         <v>22</v>
       </c>
       <c r="D19" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -4492,7 +4492,7 @@
         <v>23</v>
       </c>
       <c r="D20" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -4545,7 +4545,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -4598,7 +4598,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -4654,7 +4654,7 @@
         <v>26</v>
       </c>
       <c r="D23" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -4710,7 +4710,7 @@
         <v>27</v>
       </c>
       <c r="D24" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -4763,7 +4763,7 @@
         <v>28</v>
       </c>
       <c r="D25" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -4816,7 +4816,7 @@
         <v>29</v>
       </c>
       <c r="D26" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -4869,7 +4869,7 @@
         <v>30</v>
       </c>
       <c r="D27" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -4922,7 +4922,7 @@
         <v>31</v>
       </c>
       <c r="D28" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -4975,7 +4975,7 @@
         <v>34</v>
       </c>
       <c r="D29" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -5028,7 +5028,7 @@
         <v>35</v>
       </c>
       <c r="D30" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -5081,7 +5081,7 @@
         <v>36</v>
       </c>
       <c r="D31" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -5137,7 +5137,7 @@
         <v>37</v>
       </c>
       <c r="D32" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -5193,7 +5193,7 @@
         <v>38</v>
       </c>
       <c r="D33" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -5246,7 +5246,7 @@
         <v>39</v>
       </c>
       <c r="D34" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -5299,7 +5299,7 @@
         <v>40</v>
       </c>
       <c r="D35" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -5355,7 +5355,7 @@
         <v>213</v>
       </c>
       <c r="D36" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
